--- a/ter/dist/20261031_泰瑞達個股模型_v0.2.1.xlsx
+++ b/ter/dist/20261031_泰瑞達個股模型_v0.2.1.xlsx
@@ -4378,7 +4378,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4492,7 +4492,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4610,7 +4610,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5024,7 +5024,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5322,7 +5322,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5610,7 +5610,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5994,7 +5994,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6252,7 +6252,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6561,7 +6561,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7165,7 +7165,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7615,7 +7615,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -13409,7 +13409,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -13560,7 +13560,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
